--- a/output/parana/04_serie_temporal_mensal.xlsx
+++ b/output/parana/04_serie_temporal_mensal.xlsx
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,72 +433,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>area</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>mes_ano</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ano_mes_str</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Área</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Mês/Ano</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Ano-Mês</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>orcado_receita</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>orcado_custo</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>orcado_margem</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>receita_prevista_op</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>receita_realizada</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>custo_realizado</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>desvio_receita</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>n_registros</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>desvio_vs_orcado</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>desvio_vs_previsto</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>taxa_execucao_pct</t>
         </is>
@@ -498,7 +510,7 @@
           <t>SL01</t>
         </is>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,7 +558,7 @@
           <t>SL01</t>
         </is>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="C3" t="inlineStr">
@@ -594,7 +606,7 @@
           <t>SL01</t>
         </is>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="C4" t="inlineStr">
@@ -642,7 +654,7 @@
           <t>SL01</t>
         </is>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="C5" t="inlineStr">
@@ -690,7 +702,7 @@
           <t>SL01</t>
         </is>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="C6" t="inlineStr">
@@ -738,7 +750,7 @@
           <t>SL01</t>
         </is>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="C7" t="inlineStr">
@@ -786,7 +798,7 @@
           <t>SL01</t>
         </is>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="C8" t="inlineStr">
@@ -834,7 +846,7 @@
           <t>SL01</t>
         </is>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C9" t="inlineStr">
@@ -882,7 +894,7 @@
           <t>SL01</t>
         </is>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="C10" t="inlineStr">
@@ -930,7 +942,7 @@
           <t>SL01</t>
         </is>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="C11" t="inlineStr">
@@ -978,7 +990,7 @@
           <t>SL01</t>
         </is>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="C12" t="inlineStr">
@@ -1026,7 +1038,7 @@
           <t>SL01</t>
         </is>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="C13" t="inlineStr">
@@ -1074,7 +1086,7 @@
           <t>SL02</t>
         </is>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="C14" t="inlineStr">
@@ -1122,7 +1134,7 @@
           <t>SL02</t>
         </is>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="C15" t="inlineStr">
@@ -1170,7 +1182,7 @@
           <t>SL02</t>
         </is>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="C16" t="inlineStr">
@@ -1218,7 +1230,7 @@
           <t>SL02</t>
         </is>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="C17" t="inlineStr">
@@ -1266,7 +1278,7 @@
           <t>SL02</t>
         </is>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="C18" t="inlineStr">
@@ -1314,7 +1326,7 @@
           <t>SL02</t>
         </is>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="C19" t="inlineStr">
@@ -1362,7 +1374,7 @@
           <t>SL02</t>
         </is>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="C20" t="inlineStr">
@@ -1410,7 +1422,7 @@
           <t>SL02</t>
         </is>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C21" t="inlineStr">
@@ -1458,7 +1470,7 @@
           <t>SL02</t>
         </is>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="C22" t="inlineStr">
@@ -1506,7 +1518,7 @@
           <t>SL02</t>
         </is>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="C23" t="inlineStr">
@@ -1554,7 +1566,7 @@
           <t>SL02</t>
         </is>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="C24" t="inlineStr">
@@ -1602,7 +1614,7 @@
           <t>SL02</t>
         </is>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="C25" t="inlineStr">
